--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR INCLINAÇÃO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR INCLINAÇÃO.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SENSOR INCLIN IRON CG FAN TITAN150 EX ES ESD/ FALCON/ NX4000 189015</t>
+          <t>SENSOR INCLINACAO IRON CG FAN TITAN150 EX ES ESD/ FALCON/ NX4000 189015</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SENSOR INCLIN IRON XRE300/ CB300/ NXR150 189017</t>
+          <t>SENSOR INCLINACAO IRON XRE300/ CB300/ NXR150 189017</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -499,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SENSOR INCLIN IRON FACTOR125/ XT150/ YS150 FAZER/ 189013</t>
+          <t>SENSOR INCLINACAO IRON FACTOR125/ XT150/ YS150 FAZER/ 189013</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SENSOR INCLIN IRON CB250F TWISTER/ NXR160/ TITAN CG FAN160/ POP100 189022</t>
+          <t>SENSOR INCLINACAO IRON CB250F TWISTER/ NXR160/ TITAN CG FAN160/ POP100 189022</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR INCLINAÇÃO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR INCLINAÇÃO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -530,11 +510,6 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>130</t>
         </is>
       </c>
     </row>
